--- a/api/data/data_devengo/2026_gasto/1638007 Hospital del Perpetuo Socorro de.xlsx
+++ b/api/data/data_devengo/2026_gasto/1638007 Hospital del Perpetuo Socorro de.xlsx
@@ -534,7 +534,7 @@
       <c r="A5" s="4" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">martes 03 marzo 2026 17:03:18</t>
+            <t xml:space="preserve">viernes 13 marzo 2026 10:32:56</t>
           </r>
         </is>
       </c>
@@ -12736,7 +12736,7 @@
         <is/>
       </c>
       <c r="S87" s="14">
-        <v>46043.476006944664</v>
+        <v>46043.63144675922</v>
       </c>
       <c r="T87" s="11" t="inlineStr">
         <is>
@@ -12787,10 +12787,10 @@
         <v>280126.0</v>
       </c>
       <c r="AB87" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC87" s="15" t="n">
         <v>280126.0</v>
-      </c>
-      <c r="AC87" s="15" t="n">
-        <v>0.0</v>
       </c>
       <c r="AD87" s="11" t="inlineStr">
         <is/>
@@ -12936,10 +12936,10 @@
         <v>92820.0</v>
       </c>
       <c r="AB88" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC88" s="15" t="n">
         <v>92820.0</v>
-      </c>
-      <c r="AC88" s="15" t="n">
-        <v>0.0</v>
       </c>
       <c r="AD88" s="11" t="inlineStr">
         <is/>
@@ -13183,7 +13183,7 @@
         <is/>
       </c>
       <c r="S90" s="14">
-        <v>46043.47709490731</v>
+        <v>46043.63265046291</v>
       </c>
       <c r="T90" s="11" t="inlineStr">
         <is>
@@ -13234,10 +13234,10 @@
         <v>199444.0</v>
       </c>
       <c r="AB90" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC90" s="15" t="n">
         <v>199444.0</v>
-      </c>
-      <c r="AC90" s="15" t="n">
-        <v>0.0</v>
       </c>
       <c r="AD90" s="11" t="inlineStr">
         <is/>
@@ -13332,7 +13332,7 @@
         <is/>
       </c>
       <c r="S91" s="14">
-        <v>46043.477141203824</v>
+        <v>46043.63201388903</v>
       </c>
       <c r="T91" s="11" t="inlineStr">
         <is>
@@ -13383,10 +13383,10 @@
         <v>129115.0</v>
       </c>
       <c r="AB91" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC91" s="15" t="n">
         <v>129115.0</v>
-      </c>
-      <c r="AC91" s="15" t="n">
-        <v>0.0</v>
       </c>
       <c r="AD91" s="11" t="inlineStr">
         <is/>
@@ -13681,10 +13681,10 @@
         <v>132552.0</v>
       </c>
       <c r="AB93" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC93" s="15" t="n">
         <v>132552.0</v>
-      </c>
-      <c r="AC93" s="15" t="n">
-        <v>0.0</v>
       </c>
       <c r="AD93" s="11" t="inlineStr">
         <is/>
@@ -13830,10 +13830,10 @@
         <v>2633.0</v>
       </c>
       <c r="AB94" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC94" s="15" t="n">
         <v>2633.0</v>
-      </c>
-      <c r="AC94" s="15" t="n">
-        <v>0.0</v>
       </c>
       <c r="AD94" s="11" t="inlineStr">
         <is/>
@@ -14575,10 +14575,10 @@
         <v>29750.0</v>
       </c>
       <c r="AB99" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC99" s="15" t="n">
         <v>29750.0</v>
-      </c>
-      <c r="AC99" s="15" t="n">
-        <v>0.0</v>
       </c>
       <c r="AD99" s="11" t="inlineStr">
         <is/>
@@ -31309,10 +31309,10 @@
         <v>107457.0</v>
       </c>
       <c r="AB213" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC213" s="15" t="n">
         <v>107457.0</v>
-      </c>
-      <c r="AC213" s="15" t="n">
-        <v>0.0</v>
       </c>
       <c r="AD213" s="11" t="inlineStr">
         <is/>
@@ -31458,10 +31458,10 @@
         <v>20944.0</v>
       </c>
       <c r="AB214" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC214" s="15" t="n">
         <v>20944.0</v>
-      </c>
-      <c r="AC214" s="15" t="n">
-        <v>0.0</v>
       </c>
       <c r="AD214" s="11" t="inlineStr">
         <is/>
@@ -31607,10 +31607,10 @@
         <v>108885.0</v>
       </c>
       <c r="AB215" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC215" s="15" t="n">
         <v>108885.0</v>
-      </c>
-      <c r="AC215" s="15" t="n">
-        <v>0.0</v>
       </c>
       <c r="AD215" s="11" t="inlineStr">
         <is/>
@@ -31756,10 +31756,10 @@
         <v>13923.0</v>
       </c>
       <c r="AB216" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC216" s="15" t="n">
         <v>13923.0</v>
-      </c>
-      <c r="AC216" s="15" t="n">
-        <v>0.0</v>
       </c>
       <c r="AD216" s="11" t="inlineStr">
         <is/>
@@ -73402,50 +73402,5708 @@
         <is/>
       </c>
     </row>
-    <row r="499" customHeight="1" ht="20">
-      <c r="A499" s="3" t="inlineStr"/>
-      <c r="B499" s="3" t="inlineStr"/>
-      <c r="C499" s="3" t="inlineStr"/>
-      <c r="D499" s="16" t="inlineStr">
+    <row r="499" customHeight="1" ht="21">
+      <c r="A499" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B499" s="11" t="n">
+        <v>571.0</v>
+      </c>
+      <c r="C499" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">njm Devenga F.119 Soc Safety Technologies SPA (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D499" s="12" t="inlineStr"/>
+      <c r="E499" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F499" s="13" t="inlineStr"/>
+      <c r="G499" s="13" t="inlineStr"/>
+      <c r="H499" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I499" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">76741763-2 SOCIEDAD SAFETY TECHNOLOGIES SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J499" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K499" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L499" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M499" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N499" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">119</t>
+          </r>
+        </is>
+      </c>
+      <c r="O499" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="P499" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="Q499" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-87-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R499" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S499" s="14">
+        <v>46084.49576388905</v>
+      </c>
+      <c r="T499" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U499" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V499" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W499" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X499" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y499" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z499" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2206001001 MANTENIMIENTO Y REPARACIÓN DE EDIFICACIONES E INST</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA499" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB499" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC499" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD499" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE499" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="500" customHeight="1" ht="21">
+      <c r="A500" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B500" s="11" t="n">
+        <v>590.0</v>
+      </c>
+      <c r="C500" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">njm Devenga BOL.338 Salvador Rumian (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D500" s="12" t="inlineStr"/>
+      <c r="E500" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F500" s="13" t="inlineStr"/>
+      <c r="G500" s="13" t="inlineStr"/>
+      <c r="H500" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I500" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">15488997-3 SALVADOR PONCIANO RUMIAN  CISTERNA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J500" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K500" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L500" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M500" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1000 Boleta de Honorarios</t>
+          </r>
+        </is>
+      </c>
+      <c r="N500" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">338</t>
+          </r>
+        </is>
+      </c>
+      <c r="O500" s="14">
+        <v>46028.0</v>
+      </c>
+      <c r="P500" s="14">
+        <v/>
+      </c>
+      <c r="Q500" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-520-AG25</t>
+          </r>
+        </is>
+      </c>
+      <c r="R500" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S500" s="14">
+        <v/>
+      </c>
+      <c r="T500" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U500" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V500" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W500" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X500" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y500" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z500" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">221100200301 Ley 18575 Pagos A Prof Y Monitores</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA500" s="15" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AB500" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC500" s="15" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AD500" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE500" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="501" customHeight="1" ht="21">
+      <c r="A501" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B501" s="11" t="n">
+        <v>638.0</v>
+      </c>
+      <c r="C501" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">njm Devenga F.891320 Lab Pasteur S.A. (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D501" s="12" t="inlineStr"/>
+      <c r="E501" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F501" s="13" t="inlineStr"/>
+      <c r="G501" s="13" t="inlineStr"/>
+      <c r="H501" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I501" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">87674400-7 LABORATORIO PASTEUR S.A.</t>
+          </r>
+        </is>
+      </c>
+      <c r="J501" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K501" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L501" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M501" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N501" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">891320</t>
+          </r>
+        </is>
+      </c>
+      <c r="O501" s="14">
+        <v>46050.0</v>
+      </c>
+      <c r="P501" s="14">
+        <v>46050.0</v>
+      </c>
+      <c r="Q501" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">621-129-SE25</t>
+          </r>
+        </is>
+      </c>
+      <c r="R501" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S501" s="14">
+        <v>46050.43034722237</v>
+      </c>
+      <c r="T501" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U501" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V501" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W501" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X501" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y501" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z501" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">220400400101 Farmacia- Compras Intermediadas</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA501" s="15" t="n">
+        <v>65450.0</v>
+      </c>
+      <c r="AB501" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC501" s="15" t="n">
+        <v>65450.0</v>
+      </c>
+      <c r="AD501" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE501" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="502" customHeight="1" ht="21">
+      <c r="A502" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B502" s="11" t="n">
+        <v>640.0</v>
+      </c>
+      <c r="C502" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 32188 / 77354932 / 621-1213-SE24 / BECRUX LABS SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D502" s="12" t="inlineStr"/>
+      <c r="E502" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F502" s="13" t="inlineStr"/>
+      <c r="G502" s="13" t="inlineStr"/>
+      <c r="H502" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I502" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77354932-K BECRUX LABS</t>
+          </r>
+        </is>
+      </c>
+      <c r="J502" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K502" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L502" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M502" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N502" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">32188</t>
+          </r>
+        </is>
+      </c>
+      <c r="O502" s="14">
+        <v>46055.0</v>
+      </c>
+      <c r="P502" s="14">
+        <v>46055.0</v>
+      </c>
+      <c r="Q502" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">621-1213-SE24</t>
+          </r>
+        </is>
+      </c>
+      <c r="R502" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S502" s="14">
+        <v>46055.45640046289</v>
+      </c>
+      <c r="T502" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U502" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V502" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W502" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X502" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y502" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z502" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">220400400101 Farmacia- Compras Intermediadas</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA502" s="15" t="n">
+        <v>10341.0</v>
+      </c>
+      <c r="AB502" s="15" t="n">
+        <v>10341.0</v>
+      </c>
+      <c r="AC502" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD502" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE502" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="503" customHeight="1" ht="21">
+      <c r="A503" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B503" s="11" t="n">
+        <v>642.0</v>
+      </c>
+      <c r="C503" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">njm Devenga F.144530 Imp y Com RE-MED SPA (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D503" s="12" t="inlineStr"/>
+      <c r="E503" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F503" s="13" t="inlineStr"/>
+      <c r="G503" s="13" t="inlineStr"/>
+      <c r="H503" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I503" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">76628610-0 IMPORTADORA Y COMERCIALIZADORA RE-MED LIMITADA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J503" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K503" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L503" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M503" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N503" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">144530</t>
+          </r>
+        </is>
+      </c>
+      <c r="O503" s="14">
+        <v>46055.0</v>
+      </c>
+      <c r="P503" s="14">
+        <v>46055.0</v>
+      </c>
+      <c r="Q503" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">621-651-SE25</t>
+          </r>
+        </is>
+      </c>
+      <c r="R503" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S503" s="14">
+        <v>46055.4633912039</v>
+      </c>
+      <c r="T503" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U503" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V503" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W503" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X503" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y503" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z503" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2204005001 Instrumental Quirúrgico</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA503" s="15" t="n">
+        <v>5593.0</v>
+      </c>
+      <c r="AB503" s="15" t="n">
+        <v>5593.0</v>
+      </c>
+      <c r="AC503" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD503" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE503" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="504" customHeight="1" ht="21">
+      <c r="A504" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B504" s="11" t="n">
+        <v>643.0</v>
+      </c>
+      <c r="C504" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 848714 / 90100000 / 1057533-79-CC26 / LINDE GAS CHILE S.A.</t>
+          </r>
+        </is>
+      </c>
+      <c r="D504" s="12" t="inlineStr"/>
+      <c r="E504" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F504" s="13" t="inlineStr"/>
+      <c r="G504" s="13" t="inlineStr"/>
+      <c r="H504" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I504" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">90100000-K LINDE GAS CHILE S.A.</t>
+          </r>
+        </is>
+      </c>
+      <c r="J504" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K504" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L504" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M504" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N504" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">848714</t>
+          </r>
+        </is>
+      </c>
+      <c r="O504" s="14">
+        <v>46078.0</v>
+      </c>
+      <c r="P504" s="14">
+        <v>46086.0</v>
+      </c>
+      <c r="Q504" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-79-CC26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R504" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S504" s="14">
+        <v>46078.49841435207</v>
+      </c>
+      <c r="T504" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U504" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V504" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W504" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X504" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y504" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z504" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2204003001 Oxigeno Y Gases Clínicos</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA504" s="15" t="n">
+        <v>565488.0</v>
+      </c>
+      <c r="AB504" s="15" t="n">
+        <v>565488.0</v>
+      </c>
+      <c r="AC504" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD504" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE504" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="505" customHeight="1" ht="21">
+      <c r="A505" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B505" s="11" t="n">
+        <v>644.0</v>
+      </c>
+      <c r="C505" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">njm Devenga F.19236 Medical Front SPA (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D505" s="12" t="inlineStr"/>
+      <c r="E505" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F505" s="13" t="inlineStr"/>
+      <c r="G505" s="13" t="inlineStr"/>
+      <c r="H505" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I505" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77649912-9 MEDICAL FRONT SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J505" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K505" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L505" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M505" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N505" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">19236</t>
+          </r>
+        </is>
+      </c>
+      <c r="O505" s="14">
+        <v>46059.0</v>
+      </c>
+      <c r="P505" s="14">
+        <v>46059.0</v>
+      </c>
+      <c r="Q505" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">621-269-SE24</t>
+          </r>
+        </is>
+      </c>
+      <c r="R505" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S505" s="14">
+        <v>46059.510937499814</v>
+      </c>
+      <c r="T505" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U505" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V505" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W505" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X505" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y505" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z505" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2204005001 Instrumental Quirúrgico</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA505" s="15" t="n">
+        <v>4879.0</v>
+      </c>
+      <c r="AB505" s="15" t="n">
+        <v>4879.0</v>
+      </c>
+      <c r="AC505" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD505" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE505" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="506" customHeight="1" ht="21">
+      <c r="A506" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B506" s="11" t="n">
+        <v>645.0</v>
+      </c>
+      <c r="C506" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 710404 / 91443000 / 1057533-620-SE25 / MARSOL S A</t>
+          </r>
+        </is>
+      </c>
+      <c r="D506" s="12" t="inlineStr"/>
+      <c r="E506" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F506" s="13" t="inlineStr"/>
+      <c r="G506" s="13" t="inlineStr"/>
+      <c r="H506" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I506" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">91443000-3 MARSOL S A</t>
+          </r>
+        </is>
+      </c>
+      <c r="J506" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K506" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L506" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M506" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N506" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">710404</t>
+          </r>
+        </is>
+      </c>
+      <c r="O506" s="14">
+        <v>46076.0</v>
+      </c>
+      <c r="P506" s="14">
+        <v>46078.0</v>
+      </c>
+      <c r="Q506" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-620-SE25</t>
+          </r>
+        </is>
+      </c>
+      <c r="R506" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S506" s="14">
+        <v>46076.52390046278</v>
+      </c>
+      <c r="T506" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U506" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V506" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W506" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X506" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y506" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z506" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2206005001 MANTENIMIENTO Y REPARACIÓN DE MÁQUINAS Y EQUIPOS D</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA506" s="15" t="n">
+        <v>889687.0</v>
+      </c>
+      <c r="AB506" s="15" t="n">
+        <v>889687.0</v>
+      </c>
+      <c r="AC506" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD506" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE506" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="507" customHeight="1" ht="21">
+      <c r="A507" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B507" s="11" t="n">
+        <v>646.0</v>
+      </c>
+      <c r="C507" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">njm Devenga F.615486 Cenabast (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D507" s="12" t="inlineStr"/>
+      <c r="E507" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F507" s="13" t="inlineStr"/>
+      <c r="G507" s="13" t="inlineStr"/>
+      <c r="H507" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I507" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">61608700-2 CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          </r>
+        </is>
+      </c>
+      <c r="J507" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K507" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L507" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M507" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0202 034 Factura Exenta Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N507" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">615486</t>
+          </r>
+        </is>
+      </c>
+      <c r="O507" s="14">
+        <v>46076.0</v>
+      </c>
+      <c r="P507" s="14">
+        <v>46076.0</v>
+      </c>
+      <c r="Q507" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2026</t>
+          </r>
+        </is>
+      </c>
+      <c r="R507" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S507" s="14">
+        <v>46076.53062500013</v>
+      </c>
+      <c r="T507" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U507" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V507" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W507" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X507" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y507" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z507" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2212999019 Servicio de Intermediacion CENABAST</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA507" s="15" t="n">
+        <v>338743.0</v>
+      </c>
+      <c r="AB507" s="15" t="n">
+        <v>338743.0</v>
+      </c>
+      <c r="AC507" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD507" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE507" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="508" customHeight="1" ht="21">
+      <c r="A508" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B508" s="11" t="n">
+        <v>647.0</v>
+      </c>
+      <c r="C508" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">njm Devenga F.145261 Imp y Com RE-MED SPA (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D508" s="12" t="inlineStr"/>
+      <c r="E508" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F508" s="13" t="inlineStr"/>
+      <c r="G508" s="13" t="inlineStr"/>
+      <c r="H508" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I508" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">76628610-0 IMPORTADORA Y COMERCIALIZADORA RE-MED LIMITADA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J508" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K508" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L508" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M508" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N508" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">145261</t>
+          </r>
+        </is>
+      </c>
+      <c r="O508" s="14">
+        <v>46077.0</v>
+      </c>
+      <c r="P508" s="14">
+        <v>46077.0</v>
+      </c>
+      <c r="Q508" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">621-651-SE25</t>
+          </r>
+        </is>
+      </c>
+      <c r="R508" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S508" s="14">
+        <v>46077.54313657386</v>
+      </c>
+      <c r="T508" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U508" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V508" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W508" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X508" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y508" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z508" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2204005002 Material de Laboratorio</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA508" s="15" t="n">
+        <v>47600.0</v>
+      </c>
+      <c r="AB508" s="15" t="n">
+        <v>47600.0</v>
+      </c>
+      <c r="AC508" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD508" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE508" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="509" customHeight="1" ht="21">
+      <c r="A509" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B509" s="11" t="n">
+        <v>648.0</v>
+      </c>
+      <c r="C509" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">njm Devenga F. 3331402 Bidfood Chile S.A. (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D509" s="12" t="inlineStr"/>
+      <c r="E509" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F509" s="13" t="inlineStr"/>
+      <c r="G509" s="13" t="inlineStr"/>
+      <c r="H509" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I509" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">76111152-3 BIDFOOD CHILE S.A.</t>
+          </r>
+        </is>
+      </c>
+      <c r="J509" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K509" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L509" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M509" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N509" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">3331402</t>
+          </r>
+        </is>
+      </c>
+      <c r="O509" s="14">
+        <v>46080.0</v>
+      </c>
+      <c r="P509" s="14">
+        <v>46080.0</v>
+      </c>
+      <c r="Q509" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-9-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R509" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S509" s="14">
+        <v>46080.54879629612</v>
+      </c>
+      <c r="T509" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U509" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V509" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W509" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X509" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y509" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z509" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2201001001 Pacientes</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA509" s="15" t="n">
+        <v>218759.0</v>
+      </c>
+      <c r="AB509" s="15" t="n">
+        <v>218759.0</v>
+      </c>
+      <c r="AC509" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD509" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE509" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="510" customHeight="1" ht="21">
+      <c r="A510" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B510" s="11" t="n">
+        <v>648.0</v>
+      </c>
+      <c r="C510" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">njm Devenga F. 3331402 Bidfood Chile S.A. (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D510" s="12" t="inlineStr"/>
+      <c r="E510" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F510" s="13" t="inlineStr"/>
+      <c r="G510" s="13" t="inlineStr"/>
+      <c r="H510" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I510" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">76111152-3 BIDFOOD CHILE S.A.</t>
+          </r>
+        </is>
+      </c>
+      <c r="J510" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K510" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L510" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M510" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N510" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">3331402</t>
+          </r>
+        </is>
+      </c>
+      <c r="O510" s="14">
+        <v>46080.0</v>
+      </c>
+      <c r="P510" s="14">
+        <v>46080.0</v>
+      </c>
+      <c r="Q510" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-9-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R510" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S510" s="14">
+        <v>46080.54879629612</v>
+      </c>
+      <c r="T510" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U510" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V510" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W510" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X510" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y510" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z510" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2201001002 Funcionarios</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA510" s="15" t="n">
+        <v>1968825.0</v>
+      </c>
+      <c r="AB510" s="15" t="n">
+        <v>1968825.0</v>
+      </c>
+      <c r="AC510" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD510" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE510" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="511" customHeight="1" ht="21">
+      <c r="A511" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B511" s="11" t="n">
+        <v>649.0</v>
+      </c>
+      <c r="C511" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 688 / 77619345 / 1057533-96-AG26 / DISTRIBUCIN DE PETRLEO LIMITADA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D511" s="12" t="inlineStr"/>
+      <c r="E511" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F511" s="13" t="inlineStr"/>
+      <c r="G511" s="13" t="inlineStr"/>
+      <c r="H511" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I511" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77619345-3 DISTRIBUCIÓN DE PETRÓLEO LIMITADA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J511" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K511" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L511" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M511" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N511" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">688</t>
+          </r>
+        </is>
+      </c>
+      <c r="O511" s="14">
+        <v>46078.0</v>
+      </c>
+      <c r="P511" s="14">
+        <v>46087.0</v>
+      </c>
+      <c r="Q511" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-96-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R511" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S511" s="14">
+        <v>46080.79030092573</v>
+      </c>
+      <c r="T511" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U511" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V511" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W511" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X511" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y511" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z511" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2203003 Para Calefacción</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA511" s="15" t="n">
+        <v>1923040.0</v>
+      </c>
+      <c r="AB511" s="15" t="n">
+        <v>1923040.0</v>
+      </c>
+      <c r="AC511" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD511" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE511" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="512" customHeight="1" ht="21">
+      <c r="A512" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B512" s="11" t="n">
+        <v>650.0</v>
+      </c>
+      <c r="C512" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 1388613 / 99509000 / 1057533-92-CC26 / I-MED S.A.</t>
+          </r>
+        </is>
+      </c>
+      <c r="D512" s="12" t="inlineStr"/>
+      <c r="E512" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F512" s="13" t="inlineStr"/>
+      <c r="G512" s="13" t="inlineStr"/>
+      <c r="H512" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I512" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">99509000-7 I-MED S A</t>
+          </r>
+        </is>
+      </c>
+      <c r="J512" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K512" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L512" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M512" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N512" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1388613</t>
+          </r>
+        </is>
+      </c>
+      <c r="O512" s="14">
+        <v>46080.0</v>
+      </c>
+      <c r="P512" s="14">
+        <v>46088.0</v>
+      </c>
+      <c r="Q512" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-92-CC26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R512" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S512" s="14">
+        <v>46080.850810185075</v>
+      </c>
+      <c r="T512" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U512" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V512" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W512" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X512" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y512" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z512" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2211003 Servicios Informáticos</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA512" s="15" t="n">
+        <v>637.0</v>
+      </c>
+      <c r="AB512" s="15" t="n">
+        <v>637.0</v>
+      </c>
+      <c r="AC512" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD512" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE512" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="513" customHeight="1" ht="21">
+      <c r="A513" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B513" s="11" t="n">
+        <v>651.0</v>
+      </c>
+      <c r="C513" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 983 / 16906109 / 1057533-107-CC26 / FRANCISCO ALEJANDRO ARRIAGADA NAHUELPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D513" s="12" t="inlineStr"/>
+      <c r="E513" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F513" s="13" t="inlineStr"/>
+      <c r="G513" s="13" t="inlineStr"/>
+      <c r="H513" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I513" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">16906109-2 FRANCISCO ALEJANDRO ARRIAGADA NAHUELPÁN</t>
+          </r>
+        </is>
+      </c>
+      <c r="J513" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K513" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L513" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M513" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N513" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">983</t>
+          </r>
+        </is>
+      </c>
+      <c r="O513" s="14">
+        <v>46083.0</v>
+      </c>
+      <c r="P513" s="14">
+        <v>46090.0</v>
+      </c>
+      <c r="Q513" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-107-CC26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R513" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S513" s="14">
+        <v>46083.55179398134</v>
+      </c>
+      <c r="T513" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U513" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V513" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W513" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X513" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y513" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z513" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2206002003 MANTENIMIENTO PREVENTIVO DE VEHÍCULOS DE TRANSPORT</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA513" s="15" t="n">
+        <v>392938.0</v>
+      </c>
+      <c r="AB513" s="15" t="n">
+        <v>392938.0</v>
+      </c>
+      <c r="AC513" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD513" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE513" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="514" customHeight="1" ht="21">
+      <c r="A514" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B514" s="11" t="n">
+        <v>652.0</v>
+      </c>
+      <c r="C514" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FE / 767 / 78063490 / 1057533-66-SE26 / SOC DE TRANSPORTES HOMAD GARCIA LIMITAD</t>
+          </r>
+        </is>
+      </c>
+      <c r="D514" s="12" t="inlineStr"/>
+      <c r="E514" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F514" s="13" t="inlineStr"/>
+      <c r="G514" s="13" t="inlineStr"/>
+      <c r="H514" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I514" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">78063490-1 SOC DE TRANSPORTES HOMAD GARCIA LIMITADA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J514" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K514" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L514" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M514" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0202 034 Factura Exenta Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N514" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">767</t>
+          </r>
+        </is>
+      </c>
+      <c r="O514" s="14">
+        <v>46085.0</v>
+      </c>
+      <c r="P514" s="14">
+        <v>46090.0</v>
+      </c>
+      <c r="Q514" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-66-SE26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R514" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S514" s="14">
+        <v>46085.69126157416</v>
+      </c>
+      <c r="T514" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U514" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V514" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W514" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X514" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y514" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z514" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2208007 Pasajes, Fletes y Bodegajes</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA514" s="15" t="n">
+        <v>3635440.0</v>
+      </c>
+      <c r="AB514" s="15" t="n">
+        <v>3635440.0</v>
+      </c>
+      <c r="AC514" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD514" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE514" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="515" customHeight="1" ht="21">
+      <c r="A515" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B515" s="11" t="n">
+        <v>653.0</v>
+      </c>
+      <c r="C515" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FE / 346 / 77172073 / 1057533-14-SE26 / BARRA &amp; MEDINA TRANSPORTES LIMITADA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D515" s="12" t="inlineStr"/>
+      <c r="E515" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F515" s="13" t="inlineStr"/>
+      <c r="G515" s="13" t="inlineStr"/>
+      <c r="H515" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I515" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77172073-0 BARRIA Y MEDINA TRANSPORTES LIMITADA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J515" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K515" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L515" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M515" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0202 034 Factura Exenta Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N515" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">346</t>
+          </r>
+        </is>
+      </c>
+      <c r="O515" s="14">
+        <v>46090.0</v>
+      </c>
+      <c r="P515" s="14">
+        <v>46091.0</v>
+      </c>
+      <c r="Q515" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-14-SE26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R515" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S515" s="14">
+        <v>46090.433993055485</v>
+      </c>
+      <c r="T515" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U515" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V515" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W515" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X515" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y515" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z515" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2208007 Pasajes, Fletes y Bodegajes</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA515" s="15" t="n">
+        <v>2797200.0</v>
+      </c>
+      <c r="AB515" s="15" t="n">
+        <v>2797200.0</v>
+      </c>
+      <c r="AC515" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD515" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE515" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="516" customHeight="1" ht="21">
+      <c r="A516" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B516" s="11" t="n">
+        <v>654.0</v>
+      </c>
+      <c r="C516" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 984 / 16906109 / 1057533-106-CC26 / FRANCISCO ALEJANDRO ARRIAGADA NAHUELPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D516" s="12" t="inlineStr"/>
+      <c r="E516" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F516" s="13" t="inlineStr"/>
+      <c r="G516" s="13" t="inlineStr"/>
+      <c r="H516" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I516" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">16906109-2 FRANCISCO ALEJANDRO ARRIAGADA NAHUELPÁN</t>
+          </r>
+        </is>
+      </c>
+      <c r="J516" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K516" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L516" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M516" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N516" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">984</t>
+          </r>
+        </is>
+      </c>
+      <c r="O516" s="14">
+        <v>46083.0</v>
+      </c>
+      <c r="P516" s="14">
+        <v>46083.0</v>
+      </c>
+      <c r="Q516" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-106-CC26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R516" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S516" s="14">
+        <v>46083.98585648136</v>
+      </c>
+      <c r="T516" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U516" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V516" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W516" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X516" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y516" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z516" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2206002004 MANTENIMIENTO CORRECTIVO DE VEHÍCULOS DE TRANSPORT</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA516" s="15" t="n">
+        <v>309941.0</v>
+      </c>
+      <c r="AB516" s="15" t="n">
+        <v>309941.0</v>
+      </c>
+      <c r="AC516" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD516" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE516" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="517" customHeight="1" ht="21">
+      <c r="A517" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B517" s="11" t="n">
+        <v>655.0</v>
+      </c>
+      <c r="C517" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">njm Devenga Memo 80 05/03/2026 Allilen Casas Bono Sala Cuna (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D517" s="12" t="inlineStr"/>
+      <c r="E517" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F517" s="13" t="inlineStr"/>
+      <c r="G517" s="13" t="inlineStr"/>
+      <c r="H517" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I517" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">15275602-K Allilen Casas Martinez</t>
+          </r>
+        </is>
+      </c>
+      <c r="J517" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K517" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L517" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M517" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2800 Documento de Negocio</t>
+          </r>
+        </is>
+      </c>
+      <c r="N517" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">80</t>
+          </r>
+        </is>
+      </c>
+      <c r="O517" s="14">
+        <v>46086.0</v>
+      </c>
+      <c r="P517" s="14">
+        <v/>
+      </c>
+      <c r="Q517" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2026</t>
+          </r>
+        </is>
+      </c>
+      <c r="R517" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S517" s="14">
+        <v/>
+      </c>
+      <c r="T517" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U517" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V517" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W517" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X517" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y517" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z517" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">220800800102 SALAS CUNAS Y/O JARDINES INFANTILES: Bonos de sala</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA517" s="15" t="n">
+        <v>298070.0</v>
+      </c>
+      <c r="AB517" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC517" s="15" t="n">
+        <v>298070.0</v>
+      </c>
+      <c r="AD517" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE517" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="518" customHeight="1" ht="21">
+      <c r="A518" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B518" s="11" t="n">
+        <v>657.0</v>
+      </c>
+      <c r="C518" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">njm Devenga Memo 80 05/03/2026 Beatriz Neira Bono Sala Cuna (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D518" s="12" t="inlineStr"/>
+      <c r="E518" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F518" s="13" t="inlineStr"/>
+      <c r="G518" s="13" t="inlineStr"/>
+      <c r="H518" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I518" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">17742730-6 BEATRIZ NEIRA PEREIRA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J518" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K518" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L518" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M518" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2800 Documento de Negocio</t>
+          </r>
+        </is>
+      </c>
+      <c r="N518" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">80</t>
+          </r>
+        </is>
+      </c>
+      <c r="O518" s="14">
+        <v>46086.0</v>
+      </c>
+      <c r="P518" s="14">
+        <v/>
+      </c>
+      <c r="Q518" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2026</t>
+          </r>
+        </is>
+      </c>
+      <c r="R518" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S518" s="14">
+        <v/>
+      </c>
+      <c r="T518" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U518" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V518" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W518" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X518" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y518" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z518" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">220800800102 SALAS CUNAS Y/O JARDINES INFANTILES: Bonos de sala</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA518" s="15" t="n">
+        <v>298070.0</v>
+      </c>
+      <c r="AB518" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC518" s="15" t="n">
+        <v>298070.0</v>
+      </c>
+      <c r="AD518" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE518" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="519" customHeight="1" ht="21">
+      <c r="A519" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B519" s="11" t="n">
+        <v>659.0</v>
+      </c>
+      <c r="C519" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 119 / 76741763 / 1057533-87-AG26 / SOCIEDAD SAFETY TECHNOLOGIES SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D519" s="12" t="inlineStr"/>
+      <c r="E519" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F519" s="13" t="inlineStr"/>
+      <c r="G519" s="13" t="inlineStr"/>
+      <c r="H519" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I519" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">76741763-2 SOCIEDAD SAFETY TECHNOLOGIES SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J519" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K519" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L519" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M519" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N519" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">119</t>
+          </r>
+        </is>
+      </c>
+      <c r="O519" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="P519" s="14">
+        <v>46092.0</v>
+      </c>
+      <c r="Q519" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-87-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R519" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S519" s="14">
+        <v>46084.45915509248</v>
+      </c>
+      <c r="T519" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U519" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V519" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W519" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X519" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y519" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z519" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2206001001 MANTENIMIENTO Y REPARACIÓN DE EDIFICACIONES E INST</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA519" s="15" t="n">
+        <v>773740.0</v>
+      </c>
+      <c r="AB519" s="15" t="n">
+        <v>773740.0</v>
+      </c>
+      <c r="AC519" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD519" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE519" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="520" customHeight="1" ht="21">
+      <c r="A520" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B520" s="11" t="n">
+        <v>660.0</v>
+      </c>
+      <c r="C520" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 19313 / 76235549 / 1057533-19-CC26 / INGELIFT INGENIERIA EN TRANSPORTE VER</t>
+          </r>
+        </is>
+      </c>
+      <c r="D520" s="12" t="inlineStr"/>
+      <c r="E520" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F520" s="13" t="inlineStr"/>
+      <c r="G520" s="13" t="inlineStr"/>
+      <c r="H520" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I520" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">76235549-3 INGELIFT INGENIERIA EN TRANSPORTE VERTICAL LIMITADA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J520" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K520" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L520" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M520" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N520" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">19313</t>
+          </r>
+        </is>
+      </c>
+      <c r="O520" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="P520" s="14">
+        <v>46092.0</v>
+      </c>
+      <c r="Q520" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-19-CC26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R520" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S520" s="14">
+        <v>46084.52375000017</v>
+      </c>
+      <c r="T520" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U520" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V520" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W520" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X520" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y520" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z520" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2206005001 MANTENIMIENTO Y REPARACIÓN DE MÁQUINAS Y EQUIPOS D</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA520" s="15" t="n">
+        <v>393890.0</v>
+      </c>
+      <c r="AB520" s="15" t="n">
+        <v>393890.0</v>
+      </c>
+      <c r="AC520" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD520" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE520" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="521" customHeight="1" ht="21">
+      <c r="A521" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B521" s="11" t="n">
+        <v>680.0</v>
+      </c>
+      <c r="C521" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">vpn Devenga F. 323 Comite de agua potable rural Currupulli (HQ)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D521" s="12" t="inlineStr"/>
+      <c r="E521" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F521" s="13" t="inlineStr"/>
+      <c r="G521" s="13" t="inlineStr"/>
+      <c r="H521" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I521" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">74745400-0 COMITE DE AGUA RURAL DE CURRUPULLI</t>
+          </r>
+        </is>
+      </c>
+      <c r="J521" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K521" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L521" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M521" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N521" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">323</t>
+          </r>
+        </is>
+      </c>
+      <c r="O521" s="14">
+        <v>46087.0</v>
+      </c>
+      <c r="P521" s="14">
+        <v>46087.0</v>
+      </c>
+      <c r="Q521" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="R521" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S521" s="14">
+        <v>46087.573819444515</v>
+      </c>
+      <c r="T521" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U521" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V521" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W521" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X521" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y521" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z521" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2205002 Agua</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA521" s="15" t="n">
+        <v>764230.0</v>
+      </c>
+      <c r="AB521" s="15" t="n">
+        <v>764230.0</v>
+      </c>
+      <c r="AC521" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD521" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE521" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="522" customHeight="1" ht="21">
+      <c r="A522" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B522" s="11" t="n">
+        <v>681.0</v>
+      </c>
+      <c r="C522" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 71162 / 77618767 / 621-499-SE24 / REDLAB S.A</t>
+          </r>
+        </is>
+      </c>
+      <c r="D522" s="12" t="inlineStr"/>
+      <c r="E522" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F522" s="13" t="inlineStr"/>
+      <c r="G522" s="13" t="inlineStr"/>
+      <c r="H522" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I522" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77618767-4 REDLAB S.A</t>
+          </r>
+        </is>
+      </c>
+      <c r="J522" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K522" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L522" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M522" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N522" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">71162</t>
+          </r>
+        </is>
+      </c>
+      <c r="O522" s="14">
+        <v>46059.0</v>
+      </c>
+      <c r="P522" s="14">
+        <v>46059.0</v>
+      </c>
+      <c r="Q522" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">621-499-SE24</t>
+          </r>
+        </is>
+      </c>
+      <c r="R522" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S522" s="14">
+        <v>46059.582592592575</v>
+      </c>
+      <c r="T522" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U522" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V522" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W522" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X522" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y522" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z522" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2204005003 Otros Insumos clínicos</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA522" s="15" t="n">
+        <v>26418.0</v>
+      </c>
+      <c r="AB522" s="15" t="n">
+        <v>26418.0</v>
+      </c>
+      <c r="AC522" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD522" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE522" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="523" customHeight="1" ht="21">
+      <c r="A523" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B523" s="11" t="n">
+        <v>682.0</v>
+      </c>
+      <c r="C523" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 70977 / 76986924 / 621-203-SE24 / MDC HEALTH SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D523" s="12" t="inlineStr"/>
+      <c r="E523" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F523" s="13" t="inlineStr"/>
+      <c r="G523" s="13" t="inlineStr"/>
+      <c r="H523" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I523" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">76986924-7 MDC HEALTH SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J523" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K523" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L523" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M523" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N523" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">70977</t>
+          </r>
+        </is>
+      </c>
+      <c r="O523" s="14">
+        <v>46072.0</v>
+      </c>
+      <c r="P523" s="14">
+        <v>46072.0</v>
+      </c>
+      <c r="Q523" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">621-203-SE24</t>
+          </r>
+        </is>
+      </c>
+      <c r="R523" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S523" s="14">
+        <v>46072.697650462855</v>
+      </c>
+      <c r="T523" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U523" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V523" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W523" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X523" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y523" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z523" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">220400400101 Farmacia- Compras Intermediadas</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA523" s="15" t="n">
+        <v>46053.0</v>
+      </c>
+      <c r="AB523" s="15" t="n">
+        <v>46053.0</v>
+      </c>
+      <c r="AC523" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD523" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE523" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="524" customHeight="1" ht="21">
+      <c r="A524" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B524" s="11" t="n">
+        <v>683.0</v>
+      </c>
+      <c r="C524" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 71572 / 76986924 / 621-174-SE25 / MDC HEALTH SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D524" s="12" t="inlineStr"/>
+      <c r="E524" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F524" s="13" t="inlineStr"/>
+      <c r="G524" s="13" t="inlineStr"/>
+      <c r="H524" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I524" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">76986924-7 MDC HEALTH SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J524" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K524" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L524" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M524" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N524" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">71572</t>
+          </r>
+        </is>
+      </c>
+      <c r="O524" s="14">
+        <v>46078.0</v>
+      </c>
+      <c r="P524" s="14">
+        <v>46078.0</v>
+      </c>
+      <c r="Q524" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">621-174-SE25</t>
+          </r>
+        </is>
+      </c>
+      <c r="R524" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S524" s="14">
+        <v>46078.698784722015</v>
+      </c>
+      <c r="T524" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U524" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V524" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W524" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X524" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y524" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z524" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">220400400101 Farmacia- Compras Intermediadas</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA524" s="15" t="n">
+        <v>96390.0</v>
+      </c>
+      <c r="AB524" s="15" t="n">
+        <v>96390.0</v>
+      </c>
+      <c r="AC524" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD524" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE524" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="525" customHeight="1" ht="21">
+      <c r="A525" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B525" s="11" t="n">
+        <v>684.0</v>
+      </c>
+      <c r="C525" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 17004 / 76409952 / 621-943-SE25 / DISTRIBUIDORA SICMAFARMA CHILE SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D525" s="12" t="inlineStr"/>
+      <c r="E525" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F525" s="13" t="inlineStr"/>
+      <c r="G525" s="13" t="inlineStr"/>
+      <c r="H525" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I525" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">76409952-4 DISTRIBUIDORA SICMAFARMA CHILE SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J525" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K525" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L525" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M525" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N525" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">17004</t>
+          </r>
+        </is>
+      </c>
+      <c r="O525" s="14">
+        <v>46080.0</v>
+      </c>
+      <c r="P525" s="14">
+        <v>46080.0</v>
+      </c>
+      <c r="Q525" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">621-943-SE25</t>
+          </r>
+        </is>
+      </c>
+      <c r="R525" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S525" s="14">
+        <v>46080.700000000186</v>
+      </c>
+      <c r="T525" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U525" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V525" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W525" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X525" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y525" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z525" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">220400400101 Farmacia- Compras Intermediadas</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA525" s="15" t="n">
+        <v>53550.0</v>
+      </c>
+      <c r="AB525" s="15" t="n">
+        <v>53550.0</v>
+      </c>
+      <c r="AC525" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD525" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE525" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="526" customHeight="1" ht="21">
+      <c r="A526" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B526" s="11" t="n">
+        <v>685.0</v>
+      </c>
+      <c r="C526" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 72272 / 76986924 / 621-203-SE24 / MDC HEALTH SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D526" s="12" t="inlineStr"/>
+      <c r="E526" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F526" s="13" t="inlineStr"/>
+      <c r="G526" s="13" t="inlineStr"/>
+      <c r="H526" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I526" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">76986924-7 MDC HEALTH SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J526" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K526" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L526" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M526" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N526" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">72272</t>
+          </r>
+        </is>
+      </c>
+      <c r="O526" s="14">
+        <v>46080.0</v>
+      </c>
+      <c r="P526" s="14">
+        <v>46080.0</v>
+      </c>
+      <c r="Q526" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">621-203-SE24</t>
+          </r>
+        </is>
+      </c>
+      <c r="R526" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S526" s="14">
+        <v>46080.70098379627</v>
+      </c>
+      <c r="T526" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U526" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V526" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W526" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X526" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y526" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z526" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">220400400101 Farmacia- Compras Intermediadas</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA526" s="15" t="n">
+        <v>30702.0</v>
+      </c>
+      <c r="AB526" s="15" t="n">
+        <v>30702.0</v>
+      </c>
+      <c r="AC526" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD526" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE526" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="527" customHeight="1" ht="21">
+      <c r="A527" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B527" s="11" t="n">
+        <v>686.0</v>
+      </c>
+      <c r="C527" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 1142 / 77631534 / 1057533-55-AG26 / SOCIEDAD AGUA PURIFICADA RELONCAV SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D527" s="12" t="inlineStr"/>
+      <c r="E527" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F527" s="13" t="inlineStr"/>
+      <c r="G527" s="13" t="inlineStr"/>
+      <c r="H527" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I527" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77631534-6 AGUA PURIFICADA RELONCAVÍ</t>
+          </r>
+        </is>
+      </c>
+      <c r="J527" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K527" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L527" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M527" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N527" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1142</t>
+          </r>
+        </is>
+      </c>
+      <c r="O527" s="14">
+        <v>46083.0</v>
+      </c>
+      <c r="P527" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="Q527" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-55-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R527" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S527" s="14">
+        <v>46083.3954629628</v>
+      </c>
+      <c r="T527" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U527" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V527" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W527" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X527" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y527" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z527" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2201001001 Pacientes</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA527" s="15" t="n">
+        <v>16035.0</v>
+      </c>
+      <c r="AB527" s="15" t="n">
+        <v>16035.0</v>
+      </c>
+      <c r="AC527" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD527" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE527" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="528" customHeight="1" ht="21">
+      <c r="A528" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B528" s="11" t="n">
+        <v>686.0</v>
+      </c>
+      <c r="C528" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 1142 / 77631534 / 1057533-55-AG26 / SOCIEDAD AGUA PURIFICADA RELONCAV SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D528" s="12" t="inlineStr"/>
+      <c r="E528" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F528" s="13" t="inlineStr"/>
+      <c r="G528" s="13" t="inlineStr"/>
+      <c r="H528" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I528" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77631534-6 AGUA PURIFICADA RELONCAVÍ</t>
+          </r>
+        </is>
+      </c>
+      <c r="J528" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K528" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L528" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M528" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N528" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1142</t>
+          </r>
+        </is>
+      </c>
+      <c r="O528" s="14">
+        <v>46083.0</v>
+      </c>
+      <c r="P528" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="Q528" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-55-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R528" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S528" s="14">
+        <v>46083.3954629628</v>
+      </c>
+      <c r="T528" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U528" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V528" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W528" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X528" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y528" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z528" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2201001002 Funcionarios</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA528" s="15" t="n">
+        <v>144318.0</v>
+      </c>
+      <c r="AB528" s="15" t="n">
+        <v>144318.0</v>
+      </c>
+      <c r="AC528" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD528" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE528" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="529" customHeight="1" ht="21">
+      <c r="A529" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B529" s="11" t="n">
+        <v>687.0</v>
+      </c>
+      <c r="C529" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 1143 / 77631534 / 1057533-55-AG26 / SOCIEDAD AGUA PURIFICADA RELONCAV SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D529" s="12" t="inlineStr"/>
+      <c r="E529" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F529" s="13" t="inlineStr"/>
+      <c r="G529" s="13" t="inlineStr"/>
+      <c r="H529" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I529" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77631534-6 AGUA PURIFICADA RELONCAVÍ</t>
+          </r>
+        </is>
+      </c>
+      <c r="J529" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K529" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L529" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M529" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N529" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1143</t>
+          </r>
+        </is>
+      </c>
+      <c r="O529" s="14">
+        <v>46083.0</v>
+      </c>
+      <c r="P529" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="Q529" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-55-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R529" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S529" s="14">
+        <v>46083.39798611123</v>
+      </c>
+      <c r="T529" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U529" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V529" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W529" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X529" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y529" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z529" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2201001001 Pacientes</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA529" s="15" t="n">
+        <v>16035.0</v>
+      </c>
+      <c r="AB529" s="15" t="n">
+        <v>16035.0</v>
+      </c>
+      <c r="AC529" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD529" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE529" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="530" customHeight="1" ht="21">
+      <c r="A530" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B530" s="11" t="n">
+        <v>687.0</v>
+      </c>
+      <c r="C530" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 1143 / 77631534 / 1057533-55-AG26 / SOCIEDAD AGUA PURIFICADA RELONCAV SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D530" s="12" t="inlineStr"/>
+      <c r="E530" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F530" s="13" t="inlineStr"/>
+      <c r="G530" s="13" t="inlineStr"/>
+      <c r="H530" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I530" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77631534-6 AGUA PURIFICADA RELONCAVÍ</t>
+          </r>
+        </is>
+      </c>
+      <c r="J530" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K530" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L530" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M530" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N530" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1143</t>
+          </r>
+        </is>
+      </c>
+      <c r="O530" s="14">
+        <v>46083.0</v>
+      </c>
+      <c r="P530" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="Q530" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-55-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R530" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S530" s="14">
+        <v>46083.39798611123</v>
+      </c>
+      <c r="T530" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U530" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V530" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W530" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X530" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y530" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z530" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2201001002 Funcionarios</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA530" s="15" t="n">
+        <v>144318.0</v>
+      </c>
+      <c r="AB530" s="15" t="n">
+        <v>144318.0</v>
+      </c>
+      <c r="AC530" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD530" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE530" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="531" customHeight="1" ht="21">
+      <c r="A531" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B531" s="11" t="n">
+        <v>688.0</v>
+      </c>
+      <c r="C531" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 1144 / 77631534 / 1057533-55-AG26 / SOCIEDAD AGUA PURIFICADA RELONCAV SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D531" s="12" t="inlineStr"/>
+      <c r="E531" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F531" s="13" t="inlineStr"/>
+      <c r="G531" s="13" t="inlineStr"/>
+      <c r="H531" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I531" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77631534-6 AGUA PURIFICADA RELONCAVÍ</t>
+          </r>
+        </is>
+      </c>
+      <c r="J531" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K531" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L531" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M531" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N531" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1144</t>
+          </r>
+        </is>
+      </c>
+      <c r="O531" s="14">
+        <v>46083.0</v>
+      </c>
+      <c r="P531" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="Q531" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-55-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R531" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S531" s="14">
+        <v>46083.39940972207</v>
+      </c>
+      <c r="T531" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U531" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V531" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W531" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X531" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y531" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z531" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2201001001 Pacientes</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA531" s="15" t="n">
+        <v>16035.0</v>
+      </c>
+      <c r="AB531" s="15" t="n">
+        <v>16035.0</v>
+      </c>
+      <c r="AC531" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD531" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE531" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="532" customHeight="1" ht="21">
+      <c r="A532" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B532" s="11" t="n">
+        <v>688.0</v>
+      </c>
+      <c r="C532" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 1144 / 77631534 / 1057533-55-AG26 / SOCIEDAD AGUA PURIFICADA RELONCAV SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D532" s="12" t="inlineStr"/>
+      <c r="E532" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F532" s="13" t="inlineStr"/>
+      <c r="G532" s="13" t="inlineStr"/>
+      <c r="H532" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I532" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77631534-6 AGUA PURIFICADA RELONCAVÍ</t>
+          </r>
+        </is>
+      </c>
+      <c r="J532" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K532" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L532" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M532" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N532" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1144</t>
+          </r>
+        </is>
+      </c>
+      <c r="O532" s="14">
+        <v>46083.0</v>
+      </c>
+      <c r="P532" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="Q532" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-55-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R532" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S532" s="14">
+        <v>46083.39940972207</v>
+      </c>
+      <c r="T532" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U532" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V532" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W532" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X532" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y532" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z532" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2201001002 Funcionarios</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA532" s="15" t="n">
+        <v>144318.0</v>
+      </c>
+      <c r="AB532" s="15" t="n">
+        <v>144318.0</v>
+      </c>
+      <c r="AC532" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD532" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE532" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="533" customHeight="1" ht="21">
+      <c r="A533" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B533" s="11" t="n">
+        <v>689.0</v>
+      </c>
+      <c r="C533" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 1145 / 77631534 / 1057533-55-AG26 / SOCIEDAD AGUA PURIFICADA RELONCAV SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D533" s="12" t="inlineStr"/>
+      <c r="E533" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F533" s="13" t="inlineStr"/>
+      <c r="G533" s="13" t="inlineStr"/>
+      <c r="H533" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I533" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77631534-6 AGUA PURIFICADA RELONCAVÍ</t>
+          </r>
+        </is>
+      </c>
+      <c r="J533" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K533" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L533" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M533" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N533" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1145</t>
+          </r>
+        </is>
+      </c>
+      <c r="O533" s="14">
+        <v>46083.0</v>
+      </c>
+      <c r="P533" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="Q533" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-55-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R533" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S533" s="14">
+        <v>46083.40067129629</v>
+      </c>
+      <c r="T533" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U533" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V533" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W533" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X533" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y533" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z533" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2201001001 Pacientes</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA533" s="15" t="n">
+        <v>16035.0</v>
+      </c>
+      <c r="AB533" s="15" t="n">
+        <v>16035.0</v>
+      </c>
+      <c r="AC533" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD533" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE533" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="534" customHeight="1" ht="21">
+      <c r="A534" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B534" s="11" t="n">
+        <v>689.0</v>
+      </c>
+      <c r="C534" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 1145 / 77631534 / 1057533-55-AG26 / SOCIEDAD AGUA PURIFICADA RELONCAV SPA</t>
+          </r>
+        </is>
+      </c>
+      <c r="D534" s="12" t="inlineStr"/>
+      <c r="E534" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F534" s="13" t="inlineStr"/>
+      <c r="G534" s="13" t="inlineStr"/>
+      <c r="H534" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I534" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77631534-6 AGUA PURIFICADA RELONCAVÍ</t>
+          </r>
+        </is>
+      </c>
+      <c r="J534" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K534" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L534" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M534" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N534" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1145</t>
+          </r>
+        </is>
+      </c>
+      <c r="O534" s="14">
+        <v>46083.0</v>
+      </c>
+      <c r="P534" s="14">
+        <v>46084.0</v>
+      </c>
+      <c r="Q534" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-55-AG26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R534" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S534" s="14">
+        <v>46083.40067129629</v>
+      </c>
+      <c r="T534" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U534" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V534" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W534" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X534" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y534" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z534" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2201001002 Funcionarios</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA534" s="15" t="n">
+        <v>144318.0</v>
+      </c>
+      <c r="AB534" s="15" t="n">
+        <v>144318.0</v>
+      </c>
+      <c r="AC534" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD534" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE534" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="535" customHeight="1" ht="21">
+      <c r="A535" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B535" s="11" t="n">
+        <v>690.0</v>
+      </c>
+      <c r="C535" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 8599 / 77500240 / 1057533-113-CC26 / PRODUCTORA DE TARJETAS DE IDENTIFICAC</t>
+          </r>
+        </is>
+      </c>
+      <c r="D535" s="12" t="inlineStr"/>
+      <c r="E535" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F535" s="13" t="inlineStr"/>
+      <c r="G535" s="13" t="inlineStr"/>
+      <c r="H535" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I535" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77500240-9 PRODUCTORA DE TARJETAS DE IDENTIFICACION E-MACH CARD LIMITADA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J535" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K535" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L535" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M535" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N535" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">8599</t>
+          </r>
+        </is>
+      </c>
+      <c r="O535" s="14">
+        <v>46092.0</v>
+      </c>
+      <c r="P535" s="14">
+        <v>46093.0</v>
+      </c>
+      <c r="Q535" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-113-CC26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R535" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S535" s="14">
+        <v>46092.42924768524</v>
+      </c>
+      <c r="T535" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U535" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V535" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W535" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X535" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y535" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z535" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2211003 Servicios Informáticos</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA535" s="15" t="n">
+        <v>192135.0</v>
+      </c>
+      <c r="AB535" s="15" t="n">
+        <v>192135.0</v>
+      </c>
+      <c r="AC535" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD535" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE535" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="536" customHeight="1" ht="21">
+      <c r="A536" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1638007 Hospital del Perpetuo Socorro de Quilacahuin</t>
+          </r>
+        </is>
+      </c>
+      <c r="B536" s="11" t="n">
+        <v>691.0</v>
+      </c>
+      <c r="C536" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">FA / 8600 / 77500240 / 1057533-114-CC26 / PRODUCTORA DE TARJETAS DE IDENTIFICAC</t>
+          </r>
+        </is>
+      </c>
+      <c r="D536" s="12" t="inlineStr"/>
+      <c r="E536" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">02 Gasto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F536" s="13" t="inlineStr"/>
+      <c r="G536" s="13" t="inlineStr"/>
+      <c r="H536" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="I536" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">77500240-9 PRODUCTORA DE TARJETAS DE IDENTIFICACION E-MACH CARD LIMITADA</t>
+          </r>
+        </is>
+      </c>
+      <c r="J536" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="K536" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="L536" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M536" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0102 033 Factura Electrónica</t>
+          </r>
+        </is>
+      </c>
+      <c r="N536" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">8600</t>
+          </r>
+        </is>
+      </c>
+      <c r="O536" s="14">
+        <v>46092.0</v>
+      </c>
+      <c r="P536" s="14">
+        <v>46093.0</v>
+      </c>
+      <c r="Q536" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1057533-114-CC26</t>
+          </r>
+        </is>
+      </c>
+      <c r="R536" s="10" t="inlineStr">
+        <is/>
+      </c>
+      <c r="S536" s="14">
+        <v>46092.43777777767</v>
+      </c>
+      <c r="T536" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">ProgramaPresupuestario - 01 P01-Servicio de Salud Osorno</t>
+          </r>
+        </is>
+      </c>
+      <c r="U536" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">IniciativaInversion - 00 No Aplica</t>
+          </r>
+        </is>
+      </c>
+      <c r="V536" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DetalledeTransferencias - 04 0401-PPI OPERACIONAL BASE</t>
+          </r>
+        </is>
+      </c>
+      <c r="W536" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">UnidadesDemandantes - 00 Institucional</t>
+          </r>
+        </is>
+      </c>
+      <c r="X536" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">CentrosdeResponsabilidad - 00 Sin Aplicación</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y536" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="Z536" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2211003 Servicios Informáticos</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA536" s="15" t="n">
+        <v>192135.0</v>
+      </c>
+      <c r="AB536" s="15" t="n">
+        <v>192135.0</v>
+      </c>
+      <c r="AC536" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD536" s="11" t="inlineStr">
+        <is/>
+      </c>
+      <c r="AE536" s="11" t="inlineStr">
+        <is/>
+      </c>
+    </row>
+    <row r="537" customHeight="1" ht="20">
+      <c r="A537" s="3" t="inlineStr"/>
+      <c r="B537" s="3" t="inlineStr"/>
+      <c r="C537" s="3" t="inlineStr"/>
+      <c r="D537" s="16" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Página 1 de</t>
           </r>
         </is>
       </c>
-      <c r="E499" s="17" t="inlineStr"/>
-      <c r="F499" s="18" t="inlineStr">
+      <c r="E537" s="17" t="inlineStr"/>
+      <c r="F537" s="18" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> 1</t>
           </r>
         </is>
       </c>
-      <c r="G499" s="3" t="inlineStr"/>
-      <c r="H499" s="3" t="inlineStr"/>
-      <c r="I499" s="3" t="inlineStr"/>
-      <c r="J499" s="3" t="inlineStr"/>
-      <c r="K499" s="3" t="inlineStr"/>
-      <c r="L499" s="3" t="inlineStr"/>
-      <c r="M499" s="3" t="inlineStr"/>
-      <c r="N499" s="3" t="inlineStr"/>
-      <c r="O499" s="3" t="inlineStr"/>
-      <c r="P499" s="3" t="inlineStr"/>
-      <c r="Q499" s="3" t="inlineStr"/>
-      <c r="R499" s="3" t="inlineStr"/>
-      <c r="S499" s="3" t="inlineStr"/>
-      <c r="T499" s="3" t="inlineStr"/>
-      <c r="U499" s="3" t="inlineStr"/>
-      <c r="V499" s="3" t="inlineStr"/>
-      <c r="W499" s="3" t="inlineStr"/>
-      <c r="X499" s="3" t="inlineStr"/>
-      <c r="Y499" s="3" t="inlineStr"/>
-      <c r="Z499" s="3" t="inlineStr"/>
-      <c r="AA499" s="3" t="inlineStr"/>
-      <c r="AB499" s="3" t="inlineStr"/>
-      <c r="AC499" s="3" t="inlineStr"/>
-      <c r="AD499" s="3" t="inlineStr"/>
-      <c r="AE499" s="3" t="inlineStr"/>
+      <c r="G537" s="3" t="inlineStr"/>
+      <c r="H537" s="3" t="inlineStr"/>
+      <c r="I537" s="3" t="inlineStr"/>
+      <c r="J537" s="3" t="inlineStr"/>
+      <c r="K537" s="3" t="inlineStr"/>
+      <c r="L537" s="3" t="inlineStr"/>
+      <c r="M537" s="3" t="inlineStr"/>
+      <c r="N537" s="3" t="inlineStr"/>
+      <c r="O537" s="3" t="inlineStr"/>
+      <c r="P537" s="3" t="inlineStr"/>
+      <c r="Q537" s="3" t="inlineStr"/>
+      <c r="R537" s="3" t="inlineStr"/>
+      <c r="S537" s="3" t="inlineStr"/>
+      <c r="T537" s="3" t="inlineStr"/>
+      <c r="U537" s="3" t="inlineStr"/>
+      <c r="V537" s="3" t="inlineStr"/>
+      <c r="W537" s="3" t="inlineStr"/>
+      <c r="X537" s="3" t="inlineStr"/>
+      <c r="Y537" s="3" t="inlineStr"/>
+      <c r="Z537" s="3" t="inlineStr"/>
+      <c r="AA537" s="3" t="inlineStr"/>
+      <c r="AB537" s="3" t="inlineStr"/>
+      <c r="AC537" s="3" t="inlineStr"/>
+      <c r="AD537" s="3" t="inlineStr"/>
+      <c r="AE537" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -74440,7 +80098,83 @@
     <mergeCell ref="E497:G497"/>
     <mergeCell ref="C498:D498"/>
     <mergeCell ref="E498:G498"/>
-    <mergeCell ref="D499:E499"/>
+    <mergeCell ref="C499:D499"/>
+    <mergeCell ref="E499:G499"/>
+    <mergeCell ref="C500:D500"/>
+    <mergeCell ref="E500:G500"/>
+    <mergeCell ref="C501:D501"/>
+    <mergeCell ref="E501:G501"/>
+    <mergeCell ref="C502:D502"/>
+    <mergeCell ref="E502:G502"/>
+    <mergeCell ref="C503:D503"/>
+    <mergeCell ref="E503:G503"/>
+    <mergeCell ref="C504:D504"/>
+    <mergeCell ref="E504:G504"/>
+    <mergeCell ref="C505:D505"/>
+    <mergeCell ref="E505:G505"/>
+    <mergeCell ref="C506:D506"/>
+    <mergeCell ref="E506:G506"/>
+    <mergeCell ref="C507:D507"/>
+    <mergeCell ref="E507:G507"/>
+    <mergeCell ref="C508:D508"/>
+    <mergeCell ref="E508:G508"/>
+    <mergeCell ref="C509:D509"/>
+    <mergeCell ref="E509:G509"/>
+    <mergeCell ref="C510:D510"/>
+    <mergeCell ref="E510:G510"/>
+    <mergeCell ref="C511:D511"/>
+    <mergeCell ref="E511:G511"/>
+    <mergeCell ref="C512:D512"/>
+    <mergeCell ref="E512:G512"/>
+    <mergeCell ref="C513:D513"/>
+    <mergeCell ref="E513:G513"/>
+    <mergeCell ref="C514:D514"/>
+    <mergeCell ref="E514:G514"/>
+    <mergeCell ref="C515:D515"/>
+    <mergeCell ref="E515:G515"/>
+    <mergeCell ref="C516:D516"/>
+    <mergeCell ref="E516:G516"/>
+    <mergeCell ref="C517:D517"/>
+    <mergeCell ref="E517:G517"/>
+    <mergeCell ref="C518:D518"/>
+    <mergeCell ref="E518:G518"/>
+    <mergeCell ref="C519:D519"/>
+    <mergeCell ref="E519:G519"/>
+    <mergeCell ref="C520:D520"/>
+    <mergeCell ref="E520:G520"/>
+    <mergeCell ref="C521:D521"/>
+    <mergeCell ref="E521:G521"/>
+    <mergeCell ref="C522:D522"/>
+    <mergeCell ref="E522:G522"/>
+    <mergeCell ref="C523:D523"/>
+    <mergeCell ref="E523:G523"/>
+    <mergeCell ref="C524:D524"/>
+    <mergeCell ref="E524:G524"/>
+    <mergeCell ref="C525:D525"/>
+    <mergeCell ref="E525:G525"/>
+    <mergeCell ref="C526:D526"/>
+    <mergeCell ref="E526:G526"/>
+    <mergeCell ref="C527:D527"/>
+    <mergeCell ref="E527:G527"/>
+    <mergeCell ref="C528:D528"/>
+    <mergeCell ref="E528:G528"/>
+    <mergeCell ref="C529:D529"/>
+    <mergeCell ref="E529:G529"/>
+    <mergeCell ref="C530:D530"/>
+    <mergeCell ref="E530:G530"/>
+    <mergeCell ref="C531:D531"/>
+    <mergeCell ref="E531:G531"/>
+    <mergeCell ref="C532:D532"/>
+    <mergeCell ref="E532:G532"/>
+    <mergeCell ref="C533:D533"/>
+    <mergeCell ref="E533:G533"/>
+    <mergeCell ref="C534:D534"/>
+    <mergeCell ref="E534:G534"/>
+    <mergeCell ref="C535:D535"/>
+    <mergeCell ref="E535:G535"/>
+    <mergeCell ref="C536:D536"/>
+    <mergeCell ref="E536:G536"/>
+    <mergeCell ref="D537:E537"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.0" footer="0.0"/>
   <pageSetup orientation="landscape"/>
